--- a/r5-ELGA-MOPED-361-Patient-Journey-1-Ressourcen-+-Postman-Collection/StructureDefinition-moped-ext-LDFBetragNetto.xlsx
+++ b/r5-ELGA-MOPED-361-Patient-Journey-1-Ressourcen-+-Postman-Collection/StructureDefinition-moped-ext-LDFBetragNetto.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T09:52:56+00:00</t>
+    <t>2025-02-20T19:43:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-361-Patient-Journey-1-Ressourcen-+-Postman-Collection/StructureDefinition-moped-ext-LDFBetragNetto.xlsx
+++ b/r5-ELGA-MOPED-361-Patient-Journey-1-Ressourcen-+-Postman-Collection/StructureDefinition-moped-ext-LDFBetragNetto.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T19:43:20+00:00</t>
+    <t>2025-02-20T19:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
